--- a/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
+++ b/BWI/bestwine_output/bestwine_Hong Kong SAR.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA137"/>
+  <dimension ref="A1:AA140"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
@@ -11911,6 +11911,253 @@
         </is>
       </c>
     </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>Winetian Fine Wines</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr"/>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>168907</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E138" s="2" t="inlineStr">
+        <is>
+          <t>Kwun Tong</t>
+        </is>
+      </c>
+      <c r="F138" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="G138" s="2" t="inlineStr">
+        <is>
+          <t>4/F, KOHO, 73-75 Hung To Road</t>
+        </is>
+      </c>
+      <c r="H138" s="2" t="inlineStr"/>
+      <c r="I138" s="2" t="inlineStr">
+        <is>
+          <t>https://winetian.com</t>
+        </is>
+      </c>
+      <c r="J138" s="2" t="inlineStr"/>
+      <c r="K138" s="2" t="inlineStr"/>
+      <c r="L138" s="2" t="inlineStr"/>
+      <c r="M138" s="2" t="inlineStr"/>
+      <c r="N138" s="2" t="inlineStr">
+        <is>
+          <t>sales@winetian.com</t>
+        </is>
+      </c>
+      <c r="O138" s="2" t="inlineStr"/>
+      <c r="P138" s="2" t="inlineStr"/>
+      <c r="Q138" s="2" t="inlineStr"/>
+      <c r="R138" s="2" t="inlineStr"/>
+      <c r="S138" s="2" t="inlineStr"/>
+      <c r="T138" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/winetian_asia</t>
+        </is>
+      </c>
+      <c r="U138" s="2" t="inlineStr"/>
+      <c r="V138" s="2" t="inlineStr"/>
+      <c r="W138" s="2" t="inlineStr">
+        <is>
+          <t>Natalie Lee</t>
+        </is>
+      </c>
+      <c r="X138" s="2" t="inlineStr">
+        <is>
+          <t>Sales Manager</t>
+        </is>
+      </c>
+      <c r="Y138" s="2" t="inlineStr"/>
+      <c r="Z138" s="2" t="inlineStr"/>
+      <c r="AA138" s="2" t="inlineStr">
+        <is>
+          <t>http://www.linkedin.com/in/natalie-lee-msc-iwm-97731b194</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>Andromeda Rare Wine Limited</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>Andromeda Rare Wine Limited</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>122523</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E139" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong</t>
+        </is>
+      </c>
+      <c r="F139" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong Island</t>
+        </is>
+      </c>
+      <c r="G139" s="2" t="inlineStr">
+        <is>
+          <t>108 Wellington Street, Central</t>
+        </is>
+      </c>
+      <c r="H139" s="2" t="inlineStr"/>
+      <c r="I139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.andromedawine.com</t>
+        </is>
+      </c>
+      <c r="J139" s="2" t="inlineStr"/>
+      <c r="K139" s="2" t="inlineStr"/>
+      <c r="L139" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M139" s="2" t="inlineStr"/>
+      <c r="N139" s="2" t="inlineStr">
+        <is>
+          <t>dw@andromedawine.com</t>
+        </is>
+      </c>
+      <c r="O139" s="2" t="inlineStr"/>
+      <c r="P139" s="2" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="Q139" s="2" t="inlineStr">
+        <is>
+          <t>66102901-000</t>
+        </is>
+      </c>
+      <c r="R139" s="2" t="inlineStr"/>
+      <c r="S139" s="2" t="inlineStr"/>
+      <c r="T139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/andromedawine</t>
+        </is>
+      </c>
+      <c r="U139" s="2" t="inlineStr"/>
+      <c r="V139" s="2" t="inlineStr"/>
+      <c r="W139" s="2" t="inlineStr">
+        <is>
+          <t>Bonnie Kwok</t>
+        </is>
+      </c>
+      <c r="X139" s="2" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="Y139" s="2" t="inlineStr"/>
+      <c r="Z139" s="2" t="inlineStr"/>
+      <c r="AA139" s="2" t="inlineStr">
+        <is>
+          <t>https://www.linkedin.com/in/bonnie-kwok-52790b8a/</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>Grand Glory International Limited</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>Grand Glory International Limited</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>67710</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
+        <is>
+          <t>Hong Kong SAR</t>
+        </is>
+      </c>
+      <c r="E140" s="2" t="inlineStr">
+        <is>
+          <t>Kwai Chung</t>
+        </is>
+      </c>
+      <c r="F140" s="2" t="inlineStr">
+        <is>
+          <t>New Territories</t>
+        </is>
+      </c>
+      <c r="G140" s="2" t="inlineStr">
+        <is>
+          <t>Wealthy Industrial Building, 22 Wing Yip Street, Kwai Chung</t>
+        </is>
+      </c>
+      <c r="H140" s="2" t="inlineStr"/>
+      <c r="I140" s="2" t="inlineStr">
+        <is>
+          <t>https://grandgloryint.com</t>
+        </is>
+      </c>
+      <c r="J140" s="2" t="inlineStr"/>
+      <c r="K140" s="2" t="inlineStr"/>
+      <c r="L140" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M140" s="2" t="inlineStr"/>
+      <c r="N140" s="2" t="inlineStr">
+        <is>
+          <t>Contact@grandgloryint.com</t>
+        </is>
+      </c>
+      <c r="O140" s="2" t="inlineStr"/>
+      <c r="P140" s="2" t="inlineStr">
+        <is>
+          <t>2010</t>
+        </is>
+      </c>
+      <c r="Q140" s="2" t="inlineStr">
+        <is>
+          <t>52087024-000</t>
+        </is>
+      </c>
+      <c r="R140" s="2" t="inlineStr"/>
+      <c r="S140" s="2" t="inlineStr"/>
+      <c r="T140" s="2" t="inlineStr"/>
+      <c r="U140" s="2" t="inlineStr"/>
+      <c r="V140" s="2" t="inlineStr"/>
+      <c r="W140" s="2" t="inlineStr"/>
+      <c r="X140" s="2" t="inlineStr"/>
+      <c r="Y140" s="2" t="inlineStr"/>
+      <c r="Z140" s="2" t="inlineStr"/>
+      <c r="AA140" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
